--- a/金蛛.xlsx
+++ b/金蛛.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\github_code_lib\bd_ads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB924C11-AE85-459F-81BD-3A187B873346}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98A59825-05DA-45CD-A9A9-FCB8B3EECA57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6400" yWindow="4830" windowWidth="19200" windowHeight="11170" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="计划" sheetId="4" r:id="rId1"/>
@@ -18,6 +18,11 @@
     <sheet name="关键词" sheetId="1" r:id="rId3"/>
     <sheet name="创意" sheetId="3" r:id="rId4"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">创意!$A$1:$G$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">关键词!$A$1:$D$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">广告组!$A$1:$D$1</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -75,7 +80,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -96,14 +101,6 @@
       <name val="Consolas"/>
       <family val="3"/>
     </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
-      <name val="等线"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -122,20 +119,17 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="超链接" xfId="1" builtinId="8"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -416,7 +410,7 @@
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.83203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="21.58203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -431,12 +425,13 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5CDB6695-AA3B-4151-A170-185AFB715BF9}">
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D1"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.4140625" bestFit="1" customWidth="1"/>
@@ -459,46 +454,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="C2" s="2"/>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="C3" s="2"/>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="C4" s="2"/>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="C5" s="2"/>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="C6" s="2"/>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="C7" s="2"/>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="C8" s="2"/>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="C9" s="2"/>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="C10" s="2"/>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="C11" s="2"/>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="C12" s="2"/>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="C13" s="2"/>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="C14" s="2"/>
-    </row>
   </sheetData>
+  <autoFilter ref="A1:D1" xr:uid="{5CDB6695-AA3B-4151-A170-185AFB715BF9}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -511,6 +468,7 @@
   <cols>
     <col min="1" max="1" width="19.25" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.75" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="35.9140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -529,6 +487,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:D1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -570,7 +529,9 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:G1" xr:uid="{0E2D2BAF-782B-4B9B-BB2A-3C68B88C5665}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>